--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_equip_master.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_equip_master.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_equip_master" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="80">
   <si>
     <r>
       <rPr>
@@ -460,34 +460,37 @@
     <t>1#2#4#5#6#7#8</t>
   </si>
   <si>
-    <t>全身强化都达到</t>
-  </si>
-  <si>
-    <t>1#201011#3|1#201021#3|1#206011#3|2#202011#3|2#202021#3|2#206011#3|3#201011#3|3#201021#3|3#206011#3</t>
-  </si>
-  <si>
-    <t>1#201011#6|1#201021#6|1#206011#6|2#202011#6|2#202021#6|2#206011#6|3#201011#6|3#201021#6|3#206011#6</t>
-  </si>
-  <si>
-    <t>1#201011#10|1#201021#10|1#206011#10|2#202011#10|2#202021#10|2#206011#10|3#201011#10|3#201021#10|3#206011#10</t>
-  </si>
-  <si>
-    <t>1#201011#15|1#201021#15|1#206011#15|1#200042#250|1#600001#500|2#202011#15|2#202021#15|2#206011#15|2#200042#250|2#600001#500|3#201011#15|3#201021#15|3#206011#15|3#200042#250|3#600001#500</t>
-  </si>
-  <si>
-    <t>1#201011#23|1#201021#23|1#206011#23|1#200042#500|1#600001#1000|2#202011#23|2#202021#23|2#206011#23|2#200042#500|2#600001#1000|3#201011#23|3#201021#23|3#206011#23|3#200042#500|3#600001#1000</t>
-  </si>
-  <si>
-    <t>1#201011#34|1#201021#34|1#206011#34|1#200042#1000|1#600001#1800|2#202011#34|2#202021#34|2#206011#34|2#200042#1000|2#600001#1800|3#201011#34|3#201021#34|3#206011#34|3#200042#1000|3#600001#1800</t>
-  </si>
-  <si>
-    <t>1#201011#49|1#201021#49|1#206011#49|1#200042#1500|1#600001#2800|2#202011#49|2#202021#49|2#206011#49|2#200042#1500|2#600001#2800|3#201011#49|3#201021#49|3#206011#49|3#200042#1500|3#600001#2800</t>
-  </si>
-  <si>
-    <t>1#201011#70|1#201021#70|1#206011#70|1#200042#2000|1#600001#4000|2#202011#70|2#202021#70|2#206011#70|2#200042#2000|2#600001#4000|3#201011#70|3#201021#70|3#206011#70|3#200042#2000|3#600001#4000</t>
-  </si>
-  <si>
-    <t>1#201011#100|1#201021#100|1#206011#100|1#200042#2500|1#600001#5500|2#202011#100|2#202021#100|2#206011#100|2#200042#2500|2#600001#5500|3#201011#100|3#201021#100|3#206011#100|3#200042#2500|3#600001#5500</t>
+    <t>武器/防具强化达到</t>
+  </si>
+  <si>
+    <t>1#200041#5|1#206011#5|1#200042#100|1#600001#100|2#200041#5|2#206011#5|2#200042#100|2#600001#100|3#200041#5|3#206011#5|3#200042#100|3#600001#100|4#200041#5|4#206011#5|4#200042#100|4#600001#100|5#200041#5|5#206011#5|5#200042#100|5#600001#100|6#200041#5|6#206011#5|6#200042#100|6#600001#100|7#200041#5|7#206011#5|7#200042#100|7#600001#100|</t>
+  </si>
+  <si>
+    <t>1#200041#8|1#206011#8|1#200042#100|1#600001#200|2#200041#8|2#206011#8|2#200042#100|2#600001#200|3#200041#8|3#206011#8|3#200042#100|3#600001#200|4#200041#8|4#206011#8|4#200042#100|4#600001#200|5#200041#8|5#206011#8|5#200042#100|5#600001#200|6#200041#8|6#206011#8|6#200042#100|6#600001#200|7#200041#8|7#206011#8|7#200042#100|7#600001#200|</t>
+  </si>
+  <si>
+    <t>1#200041#13|1#206011#13|1#200042#200|1#600001#300|2#200041#13|2#206011#13|2#200042#200|2#600001#300|3#200041#13|3#206011#13|3#200042#200|3#600001#300|4#200041#13|4#206011#13|4#200042#200|4#600001#300|5#200041#13|5#206011#13|5#200042#200|5#600001#300|6#200041#13|6#206011#13|6#200042#200|6#600001#300|7#200041#13|7#206011#13|7#200042#200|7#600001#300|</t>
+  </si>
+  <si>
+    <t>1#200041#18|1#206011#18|1#200042#300|1#600001#400|2#200041#18|2#206011#18|2#200042#300|2#600001#400|3#200041#18|3#206011#18|3#200042#300|3#600001#400|4#200041#18|4#206011#18|4#200042#300|4#600001#400|5#200041#18|5#206011#18|5#200042#300|5#600001#400|6#200041#18|6#206011#18|6#200042#300|6#600001#400|7#200041#18|7#206011#18|7#200042#300|7#600001#400</t>
+  </si>
+  <si>
+    <t>1#200041#23|1#206011#23|1#200042#700|1#600001#800|2#200041#23|2#206011#23|2#200042#700|2#600001#800|3#200041#23|3#206011#23|3#200042#700|3#600001#800|4#200041#23|4#206011#23|4#200042#700|4#600001#800|5#200041#23|5#206011#23|5#200042#700|5#600001#800|6#200041#23|6#206011#23|6#200042#700|6#600001#800|7#200041#23|7#206011#23|7#200042#700|7#600001#800</t>
+  </si>
+  <si>
+    <t>1#200041#28|1#206011#28|1#200042#1000|1#600001#1500|2#200041#28|2#206011#28|2#200042#1000|2#600001#1500|3#200041#28|3#206011#28|3#200042#1000|3#600001#1500|4#200041#28|4#206011#28|4#200042#1000|4#600001#1500|5#200041#28|5#206011#28|5#200042#1000|5#600001#1500|6#200041#28|6#206011#28|6#200042#1000|6#600001#1500|7#200041#28|7#206011#28|7#200042#1000|7#600001#1500</t>
+  </si>
+  <si>
+    <t>1#200041#45|1#206011#45|1#200042#1300|1#600001#2500|2#200041#45|2#206011#45|2#200042#1300|2#600001#2500|3#200041#45|3#206011#45|3#200042#1300|3#600001#2500|4#200041#45|4#206011#45|4#200042#1300|4#600001#2500|5#200041#45|5#206011#45|5#200042#1300|5#600001#2500|6#200041#45|6#206011#45|6#200042#1300|6#600001#2500|7#200041#45|7#206011#45|7#200042#1300|7#600001#2500</t>
+  </si>
+  <si>
+    <t>1#200041#68|1#206011#68|1#200042#2200|1#600001#3800|2#200041#68|2#206011#68|2#200042#2200|2#600001#3800|3#200041#68|3#206011#68|3#200042#2200|3#600001#3800|4#200041#68|4#206011#68|4#200042#2200|4#600001#3800|5#200041#68|5#206011#68|5#200042#2200|5#600001#3800|6#200041#68|6#206011#68|6#200042#2200|6#600001#3800|7#200041#68|7#206011#68|7#200042#2200|7#600001#3800</t>
+  </si>
+  <si>
+    <t>1#200041#98|1#206011#98|1#200042#2800|1#600001#5800|2#200041#98|2#206011#98|2#200042#2800|2#600001#5800|3#200041#98|3#206011#98|3#200042#2800|3#600001#5800|4#200041#98|4#206011#98|4#200042#2800|4#600001#5800|5#200041#98|5#206011#98|5#200042#2800|5#600001#5800|6#200041#98|6#206011#98|6#200042#2800|6#600001#5800|7#200041#98|7#206011#98|7#200042#2800|7#600001#5800</t>
+  </si>
+  <si>
+    <t>1#200041#1</t>
   </si>
   <si>
     <t>201011</t>
@@ -1919,7 +1922,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="7.06666666666667" style="12" customWidth="1"/>
@@ -2334,6 +2337,37 @@
       </c>
       <c r="J13" s="13"/>
       <c r="K13" s="13"/>
+    </row>
+    <row r="14" s="12" customFormat="1" ht="15" customHeight="1" spans="1:11">
+      <c r="A14" s="16">
+        <v>10010</v>
+      </c>
+      <c r="B14" s="13">
+        <v>2</v>
+      </c>
+      <c r="C14" s="13">
+        <v>-1</v>
+      </c>
+      <c r="D14" s="13">
+        <v>1</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="13">
+        <v>1</v>
+      </c>
+      <c r="H14" s="13">
+        <v>999</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2351,10 +2385,10 @@
       <c r="C7" s="1"/>
       <c r="D7" s="2"/>
       <c r="E7" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -2388,7 +2422,7 @@
         <v>201021</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -2452,7 +2486,7 @@
         <v>202011</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -2483,10 +2517,10 @@
       <c r="C11" s="1"/>
       <c r="D11" s="4"/>
       <c r="E11" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -2550,7 +2584,7 @@
         <v>206011</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -2614,7 +2648,7 @@
         <v>200042</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -2675,10 +2709,10 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
@@ -2743,7 +2777,7 @@
         <v>3</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F19" s="9">
         <v>3</v>
@@ -2773,7 +2807,7 @@
       <c r="Q19" s="10"/>
       <c r="R19" s="10"/>
       <c r="S19" s="1" t="str">
-        <f t="shared" ref="S19:S21" si="0">_xlfn.CONCAT(D19,"#",E19,"#",F19,"|",G19,"#",H19,"#",I19,"|",J19,"#",K19,"#",L19)</f>
+        <f>_xlfn.CONCAT(D19,"#",E19,"#",F19,"|",G19,"#",H19,"#",I19,"|",J19,"#",K19,"#",L19)</f>
         <v>3#201011#3|3#201021#3|3#206011#3</v>
       </c>
       <c r="T19" s="1"/>
@@ -2796,7 +2830,7 @@
         <v>3</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F20" s="9">
         <v>6</v>
@@ -2826,7 +2860,7 @@
       <c r="Q20" s="10"/>
       <c r="R20" s="10"/>
       <c r="S20" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D20,"#",E20,"#",F20,"|",G20,"#",H20,"#",I20,"|",J20,"#",K20,"#",L20)</f>
         <v>3#201011#6|3#201021#6|3#206011#6</v>
       </c>
       <c r="T20" s="1"/>
@@ -2849,7 +2883,7 @@
         <v>3</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F21" s="9">
         <v>10</v>
@@ -2879,7 +2913,7 @@
       <c r="Q21" s="10"/>
       <c r="R21" s="10"/>
       <c r="S21" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D21,"#",E21,"#",F21,"|",G21,"#",H21,"#",I21,"|",J21,"#",K21,"#",L21)</f>
         <v>3#201011#10|3#201021#10|3#206011#10</v>
       </c>
       <c r="T21" s="1"/>
@@ -2902,7 +2936,7 @@
         <v>3</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F22" s="9">
         <v>15</v>
@@ -2938,13 +2972,13 @@
         <v>3</v>
       </c>
       <c r="Q22" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R22" s="11">
         <v>500</v>
       </c>
       <c r="S22" s="1" t="str">
-        <f t="shared" ref="S22:S27" si="1">_xlfn.CONCAT(D22,"#",E22,"#",F22,"|",G22,"#",H22,"#",I22,"|",J22,"#",K22,"#",L22,"|",M22,"#",N22,"#",O22,"|",P22,"#",Q22,"#",R22)</f>
+        <f t="shared" ref="S22:S27" si="0">_xlfn.CONCAT(D22,"#",E22,"#",F22,"|",G22,"#",H22,"#",I22,"|",J22,"#",K22,"#",L22,"|",M22,"#",N22,"#",O22,"|",P22,"#",Q22,"#",R22)</f>
         <v>3#201011#15|3#201021#15|3#206011#15|3#200042#250|3#206032#500</v>
       </c>
       <c r="T22" s="1"/>
@@ -2967,7 +3001,7 @@
         <v>3</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F23" s="9">
         <v>23</v>
@@ -3003,13 +3037,13 @@
         <v>3</v>
       </c>
       <c r="Q23" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R23" s="11">
         <v>1000</v>
       </c>
       <c r="S23" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3#201011#23|3#201021#23|3#206011#23|3#200042#500|3#206032#1000</v>
       </c>
       <c r="T23" s="1"/>
@@ -3032,7 +3066,7 @@
         <v>3</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F24" s="9">
         <v>34</v>
@@ -3068,13 +3102,13 @@
         <v>3</v>
       </c>
       <c r="Q24" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R24" s="11">
         <v>1800</v>
       </c>
       <c r="S24" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3#201011#34|3#201021#34|3#206011#34|3#200042#1000|3#206032#1800</v>
       </c>
       <c r="T24" s="1"/>
@@ -3097,7 +3131,7 @@
         <v>3</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F25" s="9">
         <v>49</v>
@@ -3133,13 +3167,13 @@
         <v>3</v>
       </c>
       <c r="Q25" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R25" s="11">
         <v>2800</v>
       </c>
       <c r="S25" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3#201011#49|3#201021#49|3#206011#49|3#200042#1500|3#206032#2800</v>
       </c>
       <c r="T25" s="1"/>
@@ -3162,7 +3196,7 @@
         <v>3</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F26" s="9">
         <v>70</v>
@@ -3198,13 +3232,13 @@
         <v>3</v>
       </c>
       <c r="Q26" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R26" s="11">
         <v>4000</v>
       </c>
       <c r="S26" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3#201011#70|3#201021#70|3#206011#70|3#200042#2000|3#206032#4000</v>
       </c>
       <c r="T26" s="1"/>
@@ -3227,7 +3261,7 @@
         <v>3</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F27" s="9">
         <v>100</v>
@@ -3263,13 +3297,13 @@
         <v>3</v>
       </c>
       <c r="Q27" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R27" s="11">
         <v>5500</v>
       </c>
       <c r="S27" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3#201011#100|3#201021#100|3#206011#100|3#200042#2500|3#206032#5500</v>
       </c>
       <c r="T27" s="1"/>
@@ -3347,7 +3381,7 @@
     <row r="30" ht="16.5" spans="3:30">
       <c r="C30" s="1"/>
       <c r="D30" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
@@ -3357,7 +3391,7 @@
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
@@ -3367,7 +3401,7 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
@@ -3383,7 +3417,7 @@
     <row r="31" ht="16.5" spans="3:30">
       <c r="C31" s="1"/>
       <c r="D31" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
@@ -3393,7 +3427,7 @@
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
@@ -3403,7 +3437,7 @@
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
       <c r="T31" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
@@ -3419,7 +3453,7 @@
     <row r="32" ht="16.5" spans="3:30">
       <c r="C32" s="1"/>
       <c r="D32" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
@@ -3429,7 +3463,7 @@
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
@@ -3439,7 +3473,7 @@
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
       <c r="T32" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
@@ -3455,7 +3489,7 @@
     <row r="33" ht="16.5" spans="3:30">
       <c r="C33" s="1"/>
       <c r="D33" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
@@ -3465,7 +3499,7 @@
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
@@ -3475,7 +3509,7 @@
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
       <c r="T33" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
@@ -3491,7 +3525,7 @@
     <row r="34" ht="16.5" spans="3:30">
       <c r="C34" s="1"/>
       <c r="D34" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
@@ -3501,7 +3535,7 @@
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
@@ -3511,7 +3545,7 @@
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
       <c r="T34" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
@@ -3527,7 +3561,7 @@
     <row r="35" ht="16.5" spans="3:30">
       <c r="C35" s="1"/>
       <c r="D35" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
@@ -3537,7 +3571,7 @@
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
@@ -3547,7 +3581,7 @@
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
       <c r="T35" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
@@ -3563,7 +3597,7 @@
     <row r="36" ht="16.5" spans="3:30">
       <c r="C36" s="1"/>
       <c r="D36" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
@@ -3573,7 +3607,7 @@
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
       <c r="L36" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
@@ -3583,7 +3617,7 @@
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
       <c r="T36" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
@@ -3599,7 +3633,7 @@
     <row r="37" ht="16.5" spans="3:30">
       <c r="C37" s="1"/>
       <c r="D37" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
@@ -3609,7 +3643,7 @@
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
       <c r="L37" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
@@ -3619,7 +3653,7 @@
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
       <c r="T37" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
@@ -3635,7 +3669,7 @@
     <row r="38" ht="16.5" spans="3:30">
       <c r="C38" s="1"/>
       <c r="D38" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
@@ -3645,7 +3679,7 @@
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
       <c r="L38" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
@@ -3655,7 +3689,7 @@
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
       <c r="T38" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
@@ -3732,7 +3766,7 @@
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1" t="str">
-        <f t="shared" ref="E41:E49" si="2">_xlfn.CONCAT(D30,"|",L30,"|",T30)</f>
+        <f t="shared" ref="E41:E49" si="1">_xlfn.CONCAT(D30,"|",L30,"|",T30)</f>
         <v>1#201011#3|1#201021#3|1#206011#3|2#202011#3|2#202021#3|2#206011#3|3#201011#3|3#201021#3|3#206011#3</v>
       </c>
       <c r="F41" s="1"/>
@@ -3765,7 +3799,7 @@
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1#201011#6|1#201021#6|1#206011#6|2#202011#6|2#202021#6|2#206011#6|3#201011#6|3#201021#6|3#206011#6</v>
       </c>
       <c r="F42" s="1"/>
@@ -3798,7 +3832,7 @@
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1#201011#10|1#201021#10|1#206011#10|2#202011#10|2#202021#10|2#206011#10|3#201011#10|3#201021#10|3#206011#10</v>
       </c>
       <c r="F43" s="1"/>
@@ -3831,7 +3865,7 @@
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1#201011#15|1#201021#15|1#206011#15|1#200042#250|1#206032#500|2#202011#15|2#202021#15|2#206011#15|2#200042#250|2#206032#500|3#201011#15|3#201021#15|3#206011#15|3#200042#250|3#206032#500</v>
       </c>
       <c r="F44" s="1"/>
@@ -3864,7 +3898,7 @@
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1#201011#23|1#201021#23|1#206011#23|1#200042#500|1#206032#1000|2#202011#23|2#202021#23|2#206011#23|2#200042#500|2#206032#1000|3#201011#23|3#201021#23|3#206011#23|3#200042#500|3#206032#1000</v>
       </c>
       <c r="F45" s="1"/>
@@ -3897,7 +3931,7 @@
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1#201011#34|1#201021#34|1#206011#34|1#200042#1000|1#206032#1800|2#202011#34|2#202021#34|2#206011#34|2#200042#1000|2#206032#1800|3#201011#34|3#201021#34|3#206011#34|3#200042#1000|3#206032#1800</v>
       </c>
       <c r="F46" s="1"/>
@@ -3930,7 +3964,7 @@
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1#201011#49|1#201021#49|1#206011#49|1#200042#1500|1#206032#2800|2#202011#49|2#202021#49|2#206011#49|2#200042#1500|2#206032#2800|3#201011#49|3#201021#49|3#206011#49|3#200042#1500|3#206032#2800</v>
       </c>
       <c r="F47" s="1"/>
@@ -3963,7 +3997,7 @@
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1#201011#70|1#201021#70|1#206011#70|1#200042#2000|1#206032#4000|2#202011#70|2#202021#70|2#206011#70|2#200042#2000|2#206032#4000|3#201011#70|3#201021#70|3#206011#70|3#200042#2000|3#206032#4000</v>
       </c>
       <c r="F48" s="1"/>
@@ -3996,7 +4030,7 @@
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1#201011#100|1#201021#100|1#206011#100|1#200042#2500|1#206032#5500|2#202011#100|2#202021#100|2#206011#100|2#200042#2500|2#206032#5500|3#201011#100|3#201021#100|3#206011#100|3#200042#2500|3#206032#5500</v>
       </c>
       <c r="F49" s="1"/>
